--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484193_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484193_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>17.8432</v>
+        <v>16.6925</v>
       </c>
       <c r="E2" t="n">
-        <v>12.7313</v>
+        <v>12.1418</v>
       </c>
       <c r="F2" t="n">
-        <v>5.1119</v>
+        <v>4.5508</v>
       </c>
       <c r="G2" t="n">
         <v>7.6509</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9733</v>
+        <v>2.8227</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7856</v>
+        <v>1.1961</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1877</v>
+        <v>1.6266</v>
       </c>
       <c r="V2" t="n">
         <v>5.6238</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1838</v>
+        <v>6.12</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5161</v>
+        <v>4.312</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6677</v>
+        <v>1.808</v>
       </c>
       <c r="G3" t="n">
         <v>2.6822</v>
@@ -688,13 +688,13 @@
         <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5016</v>
+        <v>0.4379</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2438</v>
+        <v>0.0397</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2579</v>
+        <v>0.3981</v>
       </c>
       <c r="V3" t="n">
         <v>1.8097</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. MAÑES CARRETERO</t>
+          <t>J. ARNAL DIAZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9243</v>
+        <v>4.071</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2861</v>
+        <v>-1.2476</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6381</v>
+        <v>5.3186</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0669</v>
+        <v>1.5672</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2133</v>
+        <v>0.0151</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.2802</v>
+        <v>1.5521</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3597</v>
+        <v>-0.1027</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4003</v>
+        <v>-0.1454</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.0406</v>
+        <v>0.0427</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4265</v>
+        <v>1.6699</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.187</v>
+        <v>0.1605</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2396</v>
+        <v>1.5094</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1903</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9838</v>
+        <v>2.3806</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9911</v>
+        <v>1.3135</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9103</v>
+        <v>0.0454</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0808</v>
+        <v>1.2681</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>M. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2346</v>
+        <v>3.9382</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3383</v>
+        <v>1.3282</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1037</v>
+        <v>2.6101</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4204</v>
+        <v>-0.0669</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4204</v>
+        <v>2.2133</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-2.2802</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4204</v>
+        <v>0.3597</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4204</v>
+        <v>2.4003</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-2.0406</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.4265</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.187</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.2396</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.9838</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3498</v>
+        <v>2.0051</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0406</v>
+        <v>0.9523</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3092</v>
+        <v>1.0528</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5437</v>
+        <v>1.2065</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8692</v>
+        <v>1.2065</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ARNAL DIAZ</t>
+          <t>. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2182</v>
+        <v>2.7523</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.3529</v>
+        <v>0.4743</v>
       </c>
       <c r="F6" t="n">
-        <v>5.5711</v>
+        <v>2.2779</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5672</v>
+        <v>-0.1951</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0151</v>
+        <v>-0.1318</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5521</v>
+        <v>-0.0634</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1027</v>
+        <v>0.4232</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1454</v>
+        <v>0.3831</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0427</v>
+        <v>0.0402</v>
       </c>
       <c r="M6" t="n">
-        <v>1.6699</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1605</v>
+        <v>-0.5148</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5094</v>
+        <v>-0.1035</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1903</v>
+        <v>2.1822</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1903</v>
+        <v>-0.1984</v>
       </c>
       <c r="R6" t="n">
         <v>2.3806</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4607</v>
+        <v>0.7652</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0599</v>
+        <v>0.2495</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5206</v>
+        <v>0.5157</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -951,13 +951,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9442</v>
+        <v>2.7523</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0.4743</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7168</v>
+        <v>2.2779</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1951</v>
@@ -996,13 +996,13 @@
         <v>2.3806</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0429</v>
+        <v>0.7652</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9975000000000001</v>
+        <v>0.2495</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0454</v>
+        <v>0.5157</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1017,7 +1017,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>. VICENTE SABARIEGO</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1029,58 +1029,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9442</v>
+        <v>1.5716</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-2.4907</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7168</v>
+        <v>4.0623</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1951</v>
+        <v>0.873</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1318</v>
+        <v>0.8665</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0634</v>
+        <v>0.0065</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4232</v>
+        <v>-0.2462</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3831</v>
+        <v>1.1142</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0402</v>
+        <v>-1.3604</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6183999999999999</v>
+        <v>1.1192</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5148</v>
+        <v>-0.2477</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1035</v>
+        <v>1.3669</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1822</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1984</v>
+        <v>-2.3806</v>
       </c>
       <c r="R8" t="n">
         <v>2.3806</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0429</v>
+        <v>0.6986</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9975000000000001</v>
+        <v>0.1361</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0454</v>
+        <v>0.5625</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1107,67 +1107,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6536999999999999</v>
+        <v>1.4492</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8194</v>
+        <v>3.1139</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4732</v>
+        <v>-1.6648</v>
       </c>
       <c r="G9" t="n">
-        <v>0.873</v>
+        <v>2.4204</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8665</v>
+        <v>2.4204</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0065</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2462</v>
+        <v>2.4204</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1142</v>
+        <v>2.4204</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3604</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1192</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2477</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3669</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3806</v>
+        <v>-0.9919</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3806</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2193</v>
+        <v>1.5644</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1926</v>
+        <v>0.8162</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0267</v>
+        <v>0.7481</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.5437</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="10">
@@ -1185,10 +1185,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1594</v>
+        <v>0.4258</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.218</v>
+        <v>-0.9516</v>
       </c>
       <c r="F10" t="n">
         <v>1.3774</v>
@@ -1230,10 +1230,10 @@
         <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0113</v>
+        <v>0.2551</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3117</v>
+        <v>-0.0453</v>
       </c>
       <c r="U10" t="n">
         <v>0.3004</v>
@@ -1263,13 +1263,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1519</v>
+        <v>-0.3854</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2406</v>
+        <v>-1.5864</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0888</v>
+        <v>1.201</v>
       </c>
       <c r="G11" t="n">
         <v>0.5931999999999999</v>
@@ -1308,13 +1308,13 @@
         <v>1.5871</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9567</v>
+        <v>1.7231</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2301</v>
+        <v>0.8843</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7266</v>
+        <v>0.8388</v>
       </c>
       <c r="V11" t="n">
         <v>0.8692</v>
@@ -1419,13 +1419,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3246</v>
+        <v>-1.8924</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.892</v>
+        <v>-2.3195</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5673</v>
+        <v>0.4271</v>
       </c>
       <c r="G13" t="n">
         <v>-0.0157</v>
@@ -1464,13 +1464,13 @@
         <v>1.1903</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0004</v>
+        <v>1.4326</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0567</v>
+        <v>0.6292</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9437</v>
+        <v>0.8034</v>
       </c>
       <c r="V13" t="n">
         <v>-0.532</v>
@@ -1497,13 +1497,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.9683</v>
+        <v>-5.5045</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.6551</v>
+        <v>-6.6121</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6868</v>
+        <v>1.1076</v>
       </c>
       <c r="G14" t="n">
         <v>-6.4217</v>
@@ -1542,13 +1542,13 @@
         <v>1.3887</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6773</v>
+        <v>0.7865</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7481</v>
+        <v>0.2948</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0708</v>
+        <v>0.4916</v>
       </c>
       <c r="V14" t="n">
         <v>-0.266</v>
@@ -1575,13 +1575,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>27.82850000000001</v>
+        <v>31.1583</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8715</v>
+        <v>5.359700000000004</v>
       </c>
       <c r="F15" t="n">
-        <v>24.9568</v>
+        <v>25.7985</v>
       </c>
       <c r="G15" t="n">
         <v>9.6389</v>
@@ -1593,7 +1593,7 @@
         <v>-1.294</v>
       </c>
       <c r="J15" t="n">
-        <v>9.154100000000003</v>
+        <v>9.1541</v>
       </c>
       <c r="K15" t="n">
         <v>13.2929</v>
@@ -1602,7 +1602,7 @@
         <v>-4.138500000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4849</v>
+        <v>0.4849000000000004</v>
       </c>
       <c r="N15" t="n">
         <v>-2.3598</v>
@@ -1620,13 +1620,13 @@
         <v>20.2351</v>
       </c>
       <c r="S15" t="n">
-        <v>11.4269</v>
+        <v>14.7569</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7728</v>
+        <v>5.2608</v>
       </c>
       <c r="U15" t="n">
-        <v>8.654300000000001</v>
+        <v>9.495899999999999</v>
       </c>
       <c r="V15" t="n">
         <v>6.5643</v>
@@ -1653,13 +1653,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7159</v>
+        <v>1.3996</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9636</v>
+        <v>0.7595</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7523</v>
+        <v>0.6401</v>
       </c>
       <c r="G16" t="n">
         <v>1.2808</v>
@@ -1698,13 +1698,13 @@
         <v>2.7774</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9534</v>
+        <v>-1.2697</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6914</v>
+        <v>-0.8955</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.262</v>
+        <v>-0.3742</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1985</v>
@@ -1719,7 +1719,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. NDIAYE</t>
+          <t>H. RAMON AÑIBARRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1731,64 +1731,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5800999999999999</v>
+        <v>-0.1992</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1612</v>
+        <v>0.3254</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7413</v>
+        <v>-0.5246</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.5497</v>
+        <v>3.3236</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.9814</v>
+        <v>-0.2273</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4317</v>
+        <v>3.5509</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.7889</v>
+        <v>4.4124</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.9897</v>
+        <v>2.2284</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2008</v>
+        <v>2.184</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7609</v>
+        <v>-1.0888</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9917</v>
+        <v>-2.4557</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2309</v>
+        <v>1.3669</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3887</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1903</v>
+        <v>-2.9758</v>
       </c>
       <c r="R17" t="n">
-        <v>2.579</v>
+        <v>2.7774</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.136</v>
+        <v>-2.4515</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1982</v>
+        <v>-1.3772</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0622</v>
+        <v>-1.0742</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8771</v>
+        <v>-0.873</v>
       </c>
       <c r="W17" t="n">
-        <v>3.0162</v>
+        <v>0.266</v>
       </c>
       <c r="X17" t="n">
         <v>-1.139</v>
@@ -1797,7 +1797,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. RAMON AÑIBARRO</t>
+          <t>L. NDIAYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1809,64 +1809,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7859</v>
+        <v>-0.4147</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0193</v>
+        <v>-0.8754</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8052</v>
+        <v>0.4607</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3236</v>
+        <v>-2.5497</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2273</v>
+        <v>-3.9814</v>
       </c>
       <c r="I18" t="n">
-        <v>3.5509</v>
+        <v>1.4317</v>
       </c>
       <c r="J18" t="n">
-        <v>4.4124</v>
+        <v>-1.7889</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2284</v>
+        <v>-1.9897</v>
       </c>
       <c r="L18" t="n">
-        <v>2.184</v>
+        <v>0.2008</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0888</v>
+        <v>-0.7609</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.4557</v>
+        <v>-1.9917</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3669</v>
+        <v>1.2309</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9758</v>
+        <v>-1.1903</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7774</v>
+        <v>2.579</v>
       </c>
       <c r="S18" t="n">
-        <v>-3.0381</v>
+        <v>-1.1308</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.6833</v>
+        <v>-0.9124</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3548</v>
+        <v>-0.2184</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.873</v>
+        <v>1.8771</v>
       </c>
       <c r="W18" t="n">
-        <v>0.266</v>
+        <v>3.0162</v>
       </c>
       <c r="X18" t="n">
         <v>-1.139</v>
@@ -1887,13 +1887,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9664</v>
+        <v>-1.0148</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5972</v>
+        <v>-1.3932</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6309</v>
+        <v>0.3784</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3049</v>
@@ -1932,13 +1932,13 @@
         <v>0.5952</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2647</v>
+        <v>-0.3132</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6858</v>
+        <v>-0.4817</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4211</v>
+        <v>0.1686</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1953,7 +1953,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. PIQUERAS CARBONELL</t>
+          <t>D. BOTUSAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1965,73 +1965,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2106</v>
+        <v>-2.1384</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9288</v>
+        <v>0.1502</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2818</v>
+        <v>-2.2886</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3397</v>
+        <v>-0.2863</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1513</v>
+        <v>-0.9223</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.491</v>
+        <v>0.6361</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3129</v>
+        <v>0.5072</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2727</v>
+        <v>-0.66</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0402</v>
+        <v>1.1672</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6525</v>
+        <v>-0.7935</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1214</v>
+        <v>-0.2623</v>
       </c>
       <c r="O20" t="n">
         <v>-0.5312</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3968</v>
+        <v>0.1984</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5871</v>
+        <v>0.1984</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1207</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3173</v>
+        <v>-0.357</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1966</v>
+        <v>-0.2211</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.1469</v>
+        <v>-1.4724</v>
       </c>
       <c r="W20" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4129</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. BOTUSAN</t>
+          <t>A. PIQUERAS CARBONELL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2043,67 +2043,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4547</v>
+        <v>-2.4427</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0539</v>
+        <v>-1.1329</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4008</v>
+        <v>-1.3098</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2863</v>
+        <v>-0.3397</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9223</v>
+        <v>0.1513</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6361</v>
+        <v>-0.491</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5072</v>
+        <v>0.3129</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.66</v>
+        <v>0.2727</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1672</v>
+        <v>0.0402</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7935</v>
+        <v>-0.6525</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2623</v>
+        <v>-0.1214</v>
       </c>
       <c r="O21" t="n">
         <v>-0.5312</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1984</v>
+        <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8944</v>
+        <v>-0.3528</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5611</v>
+        <v>-0.5214</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3333</v>
+        <v>0.1686</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4724</v>
+        <v>-2.1469</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4724</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="22">
@@ -2121,13 +2121,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3398</v>
+        <v>-3.2479</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6675</v>
+        <v>-3.4634</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3277</v>
+        <v>0.2155</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7516</v>
@@ -2166,13 +2166,13 @@
         <v>1.5871</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1914</v>
+        <v>-1.0996</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1846</v>
+        <v>-0.9805</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0069</v>
+        <v>-0.1191</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2199,13 +2199,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6471</v>
+        <v>-4.5349</v>
       </c>
       <c r="E23" t="n">
         <v>-3.8414</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8057</v>
+        <v>-0.6935</v>
       </c>
       <c r="G23" t="n">
         <v>0.226</v>
@@ -2244,13 +2244,13 @@
         <v>2.579</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.1471</v>
+        <v>-2.0348</v>
       </c>
       <c r="T23" t="n">
         <v>-1.0655</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0816</v>
+        <v>-0.9694</v>
       </c>
       <c r="V23" t="n">
         <v>-1.139</v>
@@ -2277,13 +2277,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.4016</v>
+        <v>-5.2613</v>
       </c>
       <c r="E24" t="n">
         <v>-4.658</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7436</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-4.8045</v>
@@ -2322,13 +2322,13 @@
         <v>1.5871</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7793</v>
+        <v>-0.639</v>
       </c>
       <c r="T24" t="n">
         <v>-0.5044</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.275</v>
+        <v>-0.1347</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2065</v>
@@ -2355,13 +2355,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.3743</v>
+        <v>-9.0299</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.3149</v>
+        <v>-9.110799999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0594</v>
+        <v>0.0809</v>
       </c>
       <c r="G25" t="n">
         <v>-4.6279</v>
@@ -2400,13 +2400,13 @@
         <v>3.5709</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.9446</v>
+        <v>-2.6003</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.808</v>
+        <v>-1.6039</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.1366</v>
+        <v>-0.9963</v>
       </c>
       <c r="V25" t="n">
         <v>-1.405</v>
@@ -2433,13 +2433,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-26.8844</v>
+        <v>-26.8842</v>
       </c>
       <c r="E26" t="n">
         <v>-23.24</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.6443</v>
+        <v>-3.6442</v>
       </c>
       <c r="G26" t="n">
         <v>-9.834200000000001</v>
@@ -2466,7 +2466,7 @@
         <v>-12.9098</v>
       </c>
       <c r="O26" t="n">
-        <v>4.178700000000001</v>
+        <v>4.1787</v>
       </c>
       <c r="P26" t="n">
         <v>1.9838</v>
@@ -2478,13 +2478,13 @@
         <v>19.8386</v>
       </c>
       <c r="S26" t="n">
-        <v>-12.4697</v>
+        <v>-12.4698</v>
       </c>
       <c r="T26" t="n">
-        <v>-8.6996</v>
+        <v>-8.699499999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.7703</v>
+        <v>-3.7702</v>
       </c>
       <c r="V26" t="n">
         <v>-6.5642</v>
